--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Nifty50 Value 20 Index Fund.xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Nifty50 Value 20 Index Fund.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="89">
   <si>
     <t>ICICI Prudential Mutual Fund</t>
   </si>
@@ -22,7 +22,7 @@
     <t>ICICI Prudential Nifty50 Value 20 Index Fund</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -61,6 +61,15 @@
     <t>Listed / Awaiting Listing On Stock Exchanges</t>
   </si>
   <si>
+    <t>ICICI Bank Ltd.</t>
+  </si>
+  <si>
+    <t>INE090A01021</t>
+  </si>
+  <si>
+    <t>Banks</t>
+  </si>
+  <si>
     <t>Infosys Ltd.</t>
   </si>
   <si>
@@ -70,13 +79,13 @@
     <t>It - Software</t>
   </si>
   <si>
-    <t>ICICI Bank Ltd.</t>
-  </si>
-  <si>
-    <t>INE090A01021</t>
-  </si>
-  <si>
-    <t>Banks</t>
+    <t>ITC Ltd.</t>
+  </si>
+  <si>
+    <t>INE154A01025</t>
+  </si>
+  <si>
+    <t>Diversified Fmcg</t>
   </si>
   <si>
     <t>Tata Consultancy Services Ltd.</t>
@@ -85,15 +94,6 @@
     <t>INE467B01029</t>
   </si>
   <si>
-    <t>ITC Ltd.</t>
-  </si>
-  <si>
-    <t>INE154A01025</t>
-  </si>
-  <si>
-    <t>Diversified Fmcg</t>
-  </si>
-  <si>
     <t>State Bank Of India</t>
   </si>
   <si>
@@ -106,6 +106,15 @@
     <t>INE860A01027</t>
   </si>
   <si>
+    <t>Maruti Suzuki India Ltd.</t>
+  </si>
+  <si>
+    <t>INE585B01010</t>
+  </si>
+  <si>
+    <t>Automobiles</t>
+  </si>
+  <si>
     <t>NTPC Ltd.</t>
   </si>
   <si>
@@ -121,15 +130,27 @@
     <t>INE155A01022</t>
   </si>
   <si>
-    <t>Automobiles</t>
-  </si>
-  <si>
     <t>Power Grid Corporation Of India Ltd.</t>
   </si>
   <si>
     <t>INE752E01010</t>
   </si>
   <si>
+    <t>Grasim Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE047A01021</t>
+  </si>
+  <si>
+    <t>Cement &amp; Cement Products</t>
+  </si>
+  <si>
+    <t>Bajaj Auto Ltd.</t>
+  </si>
+  <si>
+    <t>INE917I01010</t>
+  </si>
+  <si>
     <t>Oil &amp; Natural Gas Corporation Ltd.</t>
   </si>
   <si>
@@ -139,19 +160,13 @@
     <t>Oil</t>
   </si>
   <si>
-    <t>Bajaj Auto Ltd.</t>
-  </si>
-  <si>
-    <t>INE917I01010</t>
-  </si>
-  <si>
-    <t>Grasim Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE047A01021</t>
-  </si>
-  <si>
-    <t>Cement &amp; Cement Products</t>
+    <t>Hindalco Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE038A01020</t>
+  </si>
+  <si>
+    <t>Non - Ferrous Metals</t>
   </si>
   <si>
     <t>Coal India Ltd.</t>
@@ -163,28 +178,31 @@
     <t>Consumable Fuels</t>
   </si>
   <si>
+    <t>Cipla Ltd.</t>
+  </si>
+  <si>
+    <t>INE059A01026</t>
+  </si>
+  <si>
+    <t>Pharmaceuticals &amp; Biotechnology</t>
+  </si>
+  <si>
+    <t>Dr. Reddy's Laboratories Ltd.</t>
+  </si>
+  <si>
+    <t>INE089A01031</t>
+  </si>
+  <si>
     <t>Wipro Ltd.</t>
   </si>
   <si>
     <t>INE075A01022</t>
   </si>
   <si>
-    <t>Hindalco Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE038A01020</t>
-  </si>
-  <si>
-    <t>Non - Ferrous Metals</t>
-  </si>
-  <si>
-    <t>Dr. Reddy's Laboratories Ltd.</t>
-  </si>
-  <si>
-    <t>INE089A01031</t>
-  </si>
-  <si>
-    <t>Pharmaceuticals &amp; Biotechnology</t>
+    <t>Hero Motocorp Ltd.</t>
+  </si>
+  <si>
+    <t>INE158A01026</t>
   </si>
   <si>
     <t>IndusInd Bank Ltd.</t>
@@ -193,39 +211,6 @@
     <t>INE095A01012</t>
   </si>
   <si>
-    <t>Britannia Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE216A01030</t>
-  </si>
-  <si>
-    <t>Food Products</t>
-  </si>
-  <si>
-    <t>Hero Motocorp Ltd.</t>
-  </si>
-  <si>
-    <t>INE158A01026</t>
-  </si>
-  <si>
-    <t>Bharat Petroleum Corporation Ltd.</t>
-  </si>
-  <si>
-    <t>INE029A01011</t>
-  </si>
-  <si>
-    <t>Petroleum Products</t>
-  </si>
-  <si>
-    <t>ITC Hotels Ltd</t>
-  </si>
-  <si>
-    <t>INE379A01028</t>
-  </si>
-  <si>
-    <t>Leisure Services</t>
-  </si>
-  <si>
     <t>Unlisted</t>
   </si>
   <si>
@@ -283,7 +268,7 @@
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
@@ -666,13 +651,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>71</xdr:row>
+      <xdr:row>70</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>81</xdr:row>
+      <xdr:row>80</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -690,7 +675,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="13982700"/>
+          <a:off x="666750" y="13792200"/>
           <a:ext cx="3571875" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
@@ -705,13 +690,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>86</xdr:row>
+      <xdr:row>85</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>96</xdr:row>
+      <xdr:row>95</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -729,7 +714,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="16840200"/>
+          <a:off x="666750" y="16649700"/>
           <a:ext cx="3571875" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
@@ -1063,7 +1048,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="B1:J85"/>
+  <dimension ref="B1:J84"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="21" width="10.0" collapsed="true"/>
@@ -1163,10 +1148,10 @@
         <v>13</v>
       </c>
       <c r="G5" s="9">
-        <v>9594.51</v>
+        <v>10810.65</v>
       </c>
       <c r="H5" s="10">
-        <v>1.0013278987658998</v>
+        <v>0.9967429455478998</v>
       </c>
       <c r="I5" s="9" t="s">
         <v>13</v>
@@ -1200,10 +1185,10 @@
         <v>13</v>
       </c>
       <c r="G7" s="9">
-        <v>9594.51</v>
+        <v>10810.65</v>
       </c>
       <c r="H7" s="10">
-        <v>1.0013278987658998</v>
+        <v>0.9967429455478998</v>
       </c>
       <c r="I7" s="9" t="s">
         <v>13</v>
@@ -1226,13 +1211,13 @@
         <v>17</v>
       </c>
       <c r="F8" s="14">
-        <v>77313</v>
+        <v>119813</v>
       </c>
       <c r="G8" s="15">
-        <v>1453.33</v>
+        <v>1732.26</v>
       </c>
       <c r="H8" s="16">
-        <v>0.1516763102143</v>
+        <v>0.1597145347279</v>
       </c>
       <c r="I8" s="15" t="s">
         <v>13</v>
@@ -1255,13 +1240,13 @@
         <v>20</v>
       </c>
       <c r="F9" s="14">
-        <v>113668</v>
+        <v>98857</v>
       </c>
       <c r="G9" s="15">
-        <v>1424.03</v>
+        <v>1544.84</v>
       </c>
       <c r="H9" s="16">
-        <v>0.1486184252954</v>
+        <v>0.1424343931217</v>
       </c>
       <c r="I9" s="15" t="s">
         <v>13</v>
@@ -1281,16 +1266,16 @@
         <v>13</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F10" s="14">
-        <v>26041</v>
+        <v>265974</v>
       </c>
       <c r="G10" s="15">
-        <v>1070.91</v>
+        <v>1111.9</v>
       </c>
       <c r="H10" s="16">
-        <v>0.1117651719648</v>
+        <v>0.1025172844515</v>
       </c>
       <c r="I10" s="15" t="s">
         <v>13</v>
@@ -1301,25 +1286,25 @@
     </row>
     <row r="11" spans="2:10" ht="15" customHeight="1">
       <c r="B11" s="12" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D11" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F11" s="14">
-        <v>236984</v>
+        <v>29176</v>
       </c>
       <c r="G11" s="15">
-        <v>1060.50</v>
+        <v>1010.48</v>
       </c>
       <c r="H11" s="16">
-        <v>0.1106787357189</v>
+        <v>0.0931663509241</v>
       </c>
       <c r="I11" s="15" t="s">
         <v>13</v>
@@ -1339,16 +1324,16 @@
         <v>13</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F12" s="14">
-        <v>98085</v>
+        <v>109768</v>
       </c>
       <c r="G12" s="15">
-        <v>758.10</v>
+        <v>891.65</v>
       </c>
       <c r="H12" s="16">
-        <v>0.079118858603</v>
+        <v>0.0822102137613</v>
       </c>
       <c r="I12" s="15" t="s">
         <v>13</v>
@@ -1368,16 +1353,16 @@
         <v>13</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F13" s="14">
-        <v>26975</v>
+        <v>30299</v>
       </c>
       <c r="G13" s="15">
-        <v>465.44</v>
+        <v>495.87</v>
       </c>
       <c r="H13" s="16">
-        <v>0.0485754934021</v>
+        <v>0.0457192605818</v>
       </c>
       <c r="I13" s="15" t="s">
         <v>13</v>
@@ -1400,13 +1385,13 @@
         <v>32</v>
       </c>
       <c r="F14" s="14">
-        <v>120689</v>
+        <v>3745</v>
       </c>
       <c r="G14" s="15">
-        <v>391.03</v>
+        <v>461.35</v>
       </c>
       <c r="H14" s="16">
-        <v>0.040809718084</v>
+        <v>0.042536513339</v>
       </c>
       <c r="I14" s="15" t="s">
         <v>13</v>
@@ -1429,13 +1414,13 @@
         <v>35</v>
       </c>
       <c r="F15" s="14">
-        <v>53423</v>
+        <v>135479</v>
       </c>
       <c r="G15" s="15">
-        <v>382.56</v>
+        <v>452.36</v>
       </c>
       <c r="H15" s="16">
-        <v>0.0399257493037</v>
+        <v>0.0417076344945</v>
       </c>
       <c r="I15" s="15" t="s">
         <v>13</v>
@@ -1458,13 +1443,13 @@
         <v>32</v>
       </c>
       <c r="F16" s="14">
-        <v>115459</v>
+        <v>59621</v>
       </c>
       <c r="G16" s="15">
-        <v>348.28</v>
+        <v>428.97</v>
       </c>
       <c r="H16" s="16">
-        <v>0.0363481283132</v>
+        <v>0.0395510742973</v>
       </c>
       <c r="I16" s="15" t="s">
         <v>13</v>
@@ -1484,16 +1469,16 @@
         <v>13</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F17" s="14">
-        <v>98862</v>
+        <v>129498</v>
       </c>
       <c r="G17" s="15">
-        <v>259.62</v>
+        <v>375.22</v>
       </c>
       <c r="H17" s="16">
-        <v>0.0270951564048</v>
+        <v>0.034595319248</v>
       </c>
       <c r="I17" s="15" t="s">
         <v>13</v>
@@ -1504,25 +1489,25 @@
     </row>
     <row r="18" spans="2:10" ht="15" customHeight="1">
       <c r="B18" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="C18" s="13" t="s">
+      <c r="D18" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="D18" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>35</v>
-      </c>
       <c r="F18" s="14">
-        <v>2819</v>
+        <v>10959</v>
       </c>
       <c r="G18" s="15">
-        <v>249.42</v>
+        <v>278.99</v>
       </c>
       <c r="H18" s="16">
-        <v>0.0260306367402</v>
+        <v>0.0257229042082</v>
       </c>
       <c r="I18" s="15" t="s">
         <v>13</v>
@@ -1542,16 +1527,16 @@
         <v>13</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="F19" s="14">
-        <v>9460</v>
+        <v>3160</v>
       </c>
       <c r="G19" s="15">
-        <v>237.34</v>
+        <v>271.98</v>
       </c>
       <c r="H19" s="16">
-        <v>0.0247699114903</v>
+        <v>0.0250765815497</v>
       </c>
       <c r="I19" s="15" t="s">
         <v>13</v>
@@ -1562,25 +1547,25 @@
     </row>
     <row r="20" spans="2:10" ht="15" customHeight="1">
       <c r="B20" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="C20" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="C20" s="13" t="s">
+      <c r="D20" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E20" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="D20" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>48</v>
-      </c>
       <c r="F20" s="14">
-        <v>57804</v>
+        <v>110977</v>
       </c>
       <c r="G20" s="15">
-        <v>228.85</v>
+        <v>265.68</v>
       </c>
       <c r="H20" s="16">
-        <v>0.0238838554165</v>
+        <v>0.0244957209578</v>
       </c>
       <c r="I20" s="15" t="s">
         <v>13</v>
@@ -1591,25 +1576,25 @@
     </row>
     <row r="21" spans="2:10" ht="15" customHeight="1">
       <c r="B21" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C21" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="C21" s="13" t="s">
+      <c r="D21" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="D21" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E21" s="13" t="s">
-        <v>17</v>
-      </c>
       <c r="F21" s="14">
-        <v>72170</v>
+        <v>41361</v>
       </c>
       <c r="G21" s="15">
-        <v>225.10</v>
+        <v>262.02</v>
       </c>
       <c r="H21" s="16">
-        <v>0.0234924878928</v>
+        <v>0.024158268614</v>
       </c>
       <c r="I21" s="15" t="s">
         <v>13</v>
@@ -1632,13 +1617,13 @@
         <v>53</v>
       </c>
       <c r="F22" s="14">
-        <v>37046</v>
+        <v>64890</v>
       </c>
       <c r="G22" s="15">
-        <v>220.16</v>
+        <v>257.81</v>
       </c>
       <c r="H22" s="16">
-        <v>0.0229769264081</v>
+        <v>0.0237701062185</v>
       </c>
       <c r="I22" s="15" t="s">
         <v>13</v>
@@ -1661,13 +1646,13 @@
         <v>56</v>
       </c>
       <c r="F23" s="14">
-        <v>15538</v>
+        <v>16065</v>
       </c>
       <c r="G23" s="15">
-        <v>189.15</v>
+        <v>235.46</v>
       </c>
       <c r="H23" s="16">
-        <v>0.0197405778983</v>
+        <v>0.021709434119</v>
       </c>
       <c r="I23" s="15" t="s">
         <v>13</v>
@@ -1687,16 +1672,16 @@
         <v>13</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="F24" s="14">
-        <v>16827</v>
+        <v>17424</v>
       </c>
       <c r="G24" s="15">
-        <v>166.79</v>
+        <v>218.01</v>
       </c>
       <c r="H24" s="16">
-        <v>0.01740698381</v>
+        <v>0.0201005424797</v>
       </c>
       <c r="I24" s="15" t="s">
         <v>13</v>
@@ -1716,16 +1701,16 @@
         <v>13</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>61</v>
+        <v>20</v>
       </c>
       <c r="F25" s="14">
-        <v>2994</v>
+        <v>81152</v>
       </c>
       <c r="G25" s="15">
-        <v>153.58</v>
+        <v>202.61</v>
       </c>
       <c r="H25" s="16">
-        <v>0.0160283264796</v>
+        <v>0.0186806610331</v>
       </c>
       <c r="I25" s="15" t="s">
         <v>13</v>
@@ -1736,25 +1721,25 @@
     </row>
     <row r="26" spans="2:10" ht="15" customHeight="1">
       <c r="B26" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="C26" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="C26" s="13" t="s">
-        <v>63</v>
-      </c>
       <c r="D26" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F26" s="14">
-        <v>3294</v>
+        <v>3702</v>
       </c>
       <c r="G26" s="15">
-        <v>142.93</v>
+        <v>159.53</v>
       </c>
       <c r="H26" s="16">
-        <v>0.0149168427122</v>
+        <v>0.0147086809861</v>
       </c>
       <c r="I26" s="15" t="s">
         <v>13</v>
@@ -1765,25 +1750,25 @@
     </row>
     <row r="27" spans="2:10" ht="15" customHeight="1">
       <c r="B27" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="C27" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>65</v>
-      </c>
       <c r="D27" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>66</v>
+        <v>17</v>
       </c>
       <c r="F27" s="14">
-        <v>49328</v>
+        <v>18809</v>
       </c>
       <c r="G27" s="15">
-        <v>128.8</v>
+        <v>153.66</v>
       </c>
       <c r="H27" s="16">
-        <v>0.0134421698826</v>
+        <v>0.0141674664347</v>
       </c>
       <c r="I27" s="15" t="s">
         <v>13</v>
@@ -1794,562 +1779,562 @@
     </row>
     <row r="28" spans="2:10" ht="15" customHeight="1">
       <c r="B28" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J28" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29" spans="2:10" ht="15" customHeight="1">
+      <c r="B29" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F29" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G29" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="H29" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="I29" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J29" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="30" spans="2:10" ht="15" customHeight="1">
+      <c r="B30" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J30" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31" spans="2:10" ht="15" customHeight="1">
+      <c r="B31" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="C28" s="13" t="s">
+      <c r="C31" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F31" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G31" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="H31" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="I31" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J31" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="32" spans="2:10" ht="15" customHeight="1">
+      <c r="B32" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J32" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="33" spans="2:10" ht="15" customHeight="1">
+      <c r="B33" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F33" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G33" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="H33" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="I33" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J33" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="34" spans="2:10" ht="15" customHeight="1">
+      <c r="B34" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J34" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="35" spans="2:10" ht="15" customHeight="1">
+      <c r="B35" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E28" s="13" t="s">
+      <c r="C35" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E35" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F35" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G35" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="H35" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="I35" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J35" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="36" spans="2:10" ht="15" customHeight="1">
+      <c r="B36" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J36" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="37" spans="2:10" ht="15" customHeight="1">
+      <c r="B37" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="F28" s="14">
-        <v>23681</v>
-      </c>
-      <c r="G28" s="15">
-        <v>38.59</v>
-      </c>
-      <c r="H28" s="16">
-        <v>0.0040274327311</v>
-      </c>
-      <c r="I28" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J28" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="29" spans="2:10" ht="15" customHeight="1">
-      <c r="B29" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J29" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="30" spans="2:10" ht="15" customHeight="1">
-      <c r="B30" s="7" t="s">
+      <c r="C37" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D37" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F37" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G37" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="H37" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="I37" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J37" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="38" spans="2:10" ht="15" customHeight="1">
+      <c r="B38" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J38" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="39" spans="2:10" ht="15" customHeight="1">
+      <c r="B39" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="C30" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D30" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E30" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F30" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G30" s="9" t="s">
+      <c r="C39" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D39" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F39" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G39" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="H39" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="I39" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J39" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="40" spans="2:10" ht="15" customHeight="1">
+      <c r="B40" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J40" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="41" spans="2:10" ht="15" customHeight="1">
+      <c r="B41" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="H30" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="I30" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J30" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="31" spans="2:10" ht="15" customHeight="1">
-      <c r="B31" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J31" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="32" spans="2:10" ht="15" customHeight="1">
-      <c r="B32" s="7" t="s">
+      <c r="C41" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D41" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E41" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F41" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G41" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="H41" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="I41" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J41" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="42" spans="2:10" ht="15" customHeight="1">
+      <c r="B42" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J42" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="43" spans="2:10" ht="15" customHeight="1">
+      <c r="B43" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="C32" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D32" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E32" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F32" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G32" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="H32" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="I32" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J32" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="33" spans="2:10" ht="15" customHeight="1">
-      <c r="B33" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J33" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="34" spans="2:10" ht="15" customHeight="1">
-      <c r="B34" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C34" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D34" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E34" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F34" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G34" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="H34" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="I34" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J34" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="35" spans="2:10" ht="15" customHeight="1">
-      <c r="B35" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J35" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="36" spans="2:10" ht="15" customHeight="1">
-      <c r="B36" s="7" t="s">
+      <c r="C43" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D43" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E43" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F43" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G43" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="H43" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="I43" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J43" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="44" spans="2:10" ht="15" customHeight="1">
+      <c r="B44" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J44" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="45" spans="2:10" ht="15" customHeight="1">
+      <c r="B45" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="C36" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D36" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E36" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F36" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G36" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="H36" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="I36" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J36" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="37" spans="2:10" ht="15" customHeight="1">
-      <c r="B37" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J37" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="38" spans="2:10" ht="15" customHeight="1">
-      <c r="B38" s="7" t="s">
+      <c r="C45" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F45" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G45" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="H45" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="I45" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J45" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="46" spans="2:10" ht="15" customHeight="1">
+      <c r="B46" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J46" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="47" spans="2:10" ht="15" customHeight="1">
+      <c r="B47" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="C38" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D38" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E38" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F38" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G38" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="H38" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="I38" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J38" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="39" spans="2:10" ht="15" customHeight="1">
-      <c r="B39" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J39" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="40" spans="2:10" ht="15" customHeight="1">
-      <c r="B40" s="7" t="s">
+      <c r="C47" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D47" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E47" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F47" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G47" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="H47" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="I47" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J47" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="48" spans="2:10" ht="15" customHeight="1">
+      <c r="B48" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J48" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="49" spans="2:10" ht="15" customHeight="1">
+      <c r="B49" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="C40" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D40" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E40" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F40" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G40" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="H40" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="I40" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J40" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="41" spans="2:10" ht="15" customHeight="1">
-      <c r="B41" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J41" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="42" spans="2:10" ht="15" customHeight="1">
-      <c r="B42" s="7" t="s">
+      <c r="C49" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D49" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E49" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F49" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G49" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="H49" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="I49" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J49" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="50" spans="2:10" ht="15" customHeight="1">
+      <c r="B50" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J50" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="51" spans="2:10" ht="15" customHeight="1">
+      <c r="B51" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="C42" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D42" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E42" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F42" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G42" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="H42" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="I42" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J42" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="43" spans="2:10" ht="15" customHeight="1">
-      <c r="B43" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J43" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="44" spans="2:10" ht="15" customHeight="1">
-      <c r="B44" s="7" t="s">
+      <c r="C51" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D51" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E51" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F51" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G51" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="H51" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="I51" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J51" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="52" spans="2:10" ht="15" customHeight="1">
+      <c r="B52" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J52" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="53" spans="2:10" ht="15" customHeight="1">
+      <c r="B53" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C44" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D44" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E44" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F44" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G44" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="H44" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="I44" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J44" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="45" spans="2:10" ht="15" customHeight="1">
-      <c r="B45" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J45" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="46" spans="2:10" ht="15" customHeight="1">
-      <c r="B46" s="7" t="s">
+      <c r="C53" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D53" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E53" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F53" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G53" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="H53" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="I53" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J53" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="54" spans="2:10" ht="15" customHeight="1">
+      <c r="B54" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J54" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="55" spans="2:10" ht="15" customHeight="1">
+      <c r="B55" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="C46" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D46" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E46" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F46" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G46" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="H46" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="I46" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J46" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="47" spans="2:10" ht="15" customHeight="1">
-      <c r="B47" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J47" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="48" spans="2:10" ht="15" customHeight="1">
-      <c r="B48" s="7" t="s">
+      <c r="C55" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D55" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E55" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F55" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G55" s="9">
+        <v>26.41</v>
+      </c>
+      <c r="H55" s="10">
+        <v>0.0024350044809</v>
+      </c>
+      <c r="I55" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J55" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="56" spans="2:10" ht="15" customHeight="1">
+      <c r="B56" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J56" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="57" spans="2:10" ht="15" customHeight="1">
+      <c r="B57" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="C48" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D48" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E48" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F48" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G48" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="H48" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="I48" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J48" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="49" spans="2:10" ht="15" customHeight="1">
-      <c r="B49" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J49" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="50" spans="2:10" ht="15" customHeight="1">
-      <c r="B50" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="C50" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D50" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E50" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F50" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G50" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="H50" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="I50" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J50" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="51" spans="2:10" ht="15" customHeight="1">
-      <c r="B51" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J51" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="52" spans="2:10" ht="15" customHeight="1">
-      <c r="B52" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="C52" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D52" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E52" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F52" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G52" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="H52" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="I52" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J52" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="53" spans="2:10" ht="15" customHeight="1">
-      <c r="B53" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J53" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="54" spans="2:10" ht="15" customHeight="1">
-      <c r="B54" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="C54" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D54" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E54" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F54" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G54" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="H54" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="I54" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J54" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="55" spans="2:10" ht="15" customHeight="1">
-      <c r="B55" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J55" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="56" spans="2:10" ht="15" customHeight="1">
-      <c r="B56" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="C56" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D56" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E56" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F56" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G56" s="9">
-        <v>168.86</v>
-      </c>
-      <c r="H56" s="10">
-        <v>0.0176230186831</v>
-      </c>
-      <c r="I56" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J56" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="57" spans="2:10" ht="15" customHeight="1">
-      <c r="B57" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J57" s="11" t="s">
+      <c r="C57" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D57" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E57" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F57" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G57" s="18">
+        <v>8.91593419000128</v>
+      </c>
+      <c r="H57" s="19">
+        <v>0.0008220499698782653</v>
+      </c>
+      <c r="I57" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="J57" s="20" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="58" spans="2:10" ht="15" customHeight="1">
       <c r="B58" s="17" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C58" s="18" t="s">
         <v>13</v>
@@ -2364,10 +2349,10 @@
         <v>13</v>
       </c>
       <c r="G58" s="18">
-        <v>-181.58364229000108</v>
+        <v>10845.97593419</v>
       </c>
       <c r="H58" s="19">
-        <v>-0.01895091745015683</v>
+        <v>0.999999999998678</v>
       </c>
       <c r="I58" s="18" t="s">
         <v>13</v>
@@ -2376,38 +2361,21 @@
         <v>13</v>
       </c>
     </row>
-    <row r="59" spans="2:10" ht="15" customHeight="1">
-      <c r="B59" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="C59" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D59" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="E59" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F59" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G59" s="18">
-        <v>9581.78635771</v>
-      </c>
-      <c r="H59" s="19">
-        <v>0.999999999998843</v>
-      </c>
-      <c r="I59" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="J59" s="20" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="62" spans="2:9" ht="15" customHeight="1">
+    <row r="61" spans="2:9" ht="15" customHeight="1">
+      <c r="B61" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="C61" s="21"/>
+      <c r="D61" s="21"/>
+      <c r="E61" s="21"/>
+      <c r="F61" s="21"/>
+      <c r="G61" s="21"/>
+      <c r="H61" s="21"/>
+      <c r="I61" s="21"/>
+    </row>
+    <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="13" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C62" s="21"/>
       <c r="D62" s="21"/>
@@ -2415,11 +2383,10 @@
       <c r="F62" s="21"/>
       <c r="G62" s="21"/>
       <c r="H62" s="21"/>
-      <c r="I62" s="21"/>
-    </row>
-    <row r="63" spans="2:8" ht="15" customHeight="1">
-      <c r="B63" s="13" t="s">
-        <v>87</v>
+    </row>
+    <row r="63" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B63" s="22" t="s">
+        <v>83</v>
       </c>
       <c r="C63" s="21"/>
       <c r="D63" s="21"/>
@@ -2430,7 +2397,7 @@
     </row>
     <row r="64" spans="2:8" ht="27.6" customHeight="1">
       <c r="B64" s="22" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C64" s="21"/>
       <c r="D64" s="21"/>
@@ -2441,7 +2408,7 @@
     </row>
     <row r="65" spans="2:8" ht="27.6" customHeight="1">
       <c r="B65" s="22" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C65" s="21"/>
       <c r="D65" s="21"/>
@@ -2450,42 +2417,31 @@
       <c r="G65" s="21"/>
       <c r="H65" s="21"/>
     </row>
-    <row r="66" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B66" s="22" t="s">
-        <v>90</v>
-      </c>
-      <c r="C66" s="21"/>
-      <c r="D66" s="21"/>
-      <c r="E66" s="21"/>
-      <c r="F66" s="21"/>
-      <c r="G66" s="21"/>
-      <c r="H66" s="21"/>
-    </row>
-    <row r="69" ht="15">
-      <c r="B69" s="21" t="s">
-        <v>91</v>
+    <row r="68" ht="15">
+      <c r="B68" s="21" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="83" ht="15">
+      <c r="B83" s="21" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="84" ht="15">
       <c r="B84" s="21" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="85" ht="15">
-      <c r="B85" s="21" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="B63:H63"/>
     <mergeCell ref="B64:H64"/>
     <mergeCell ref="B65:H65"/>
-    <mergeCell ref="B66:H66"/>
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B62:I62"/>
-    <mergeCell ref="B63:H63"/>
+    <mergeCell ref="B61:I61"/>
+    <mergeCell ref="B62:H62"/>
   </mergeCells>
   <printOptions gridLines="1" headings="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
